--- a/converted/oylik/2026-01/Elektr Podstansiyalar.xlsx
+++ b/converted/oylik/2026-01/Elektr Podstansiyalar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Podstansiyalar Yanvar Holatiga Ko'ra</t>
   </si>
@@ -49,12 +49,21 @@
     <t>Umumiy oqim (7 oylik jami)</t>
   </si>
   <si>
+    <t>Umumiy oqim (podstansiya faylida)</t>
+  </si>
+  <si>
     <t>Foydali oqim (7 oylik jami)</t>
   </si>
   <si>
+    <t>Foydali oqim (podstansiya faylida)</t>
+  </si>
+  <si>
     <t>Yo’qotish (7 oylik jami)</t>
   </si>
   <si>
+    <t>Yo’qotish (podstansiya faylida)</t>
+  </si>
+  <si>
     <t>Manzil (manba)</t>
   </si>
   <si>
@@ -67,6 +76,9 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -121,6 +133,9 @@
     <t>110 kV</t>
   </si>
   <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Podstansiyalar.xlsx [7 oylik], 3-qator</t>
   </si>
   <si>
@@ -143,6 +158,12 @@
   </si>
   <si>
     <t>chinobod/Elektr Podstansiyalar.xlsx [7 oylik], 4-qator</t>
+  </si>
+  <si>
+    <t>Oltinko'l</t>
+  </si>
+  <si>
+    <t>transformatorlar.xlsx [Yanvar], 41-qator</t>
   </si>
 </sst>
 </file>
@@ -561,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -570,10 +591,10 @@
     <col min="6" max="7" width="16" style="2" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="18" width="26" customWidth="1"/>
+    <col min="10" max="22" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -594,8 +615,12 @@
       <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" ht="45" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -650,22 +675,34 @@
       <c r="R2" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="S2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1">
-        <v>1203315.29</v>
+        <v>1791420.938457</v>
       </c>
       <c r="C3" s="1">
-        <v>1041589.57</v>
+        <v>1300019.384848</v>
       </c>
       <c r="D3" s="1">
-        <v>161725.57</v>
+        <v>491401.553609</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2">
         <v>40.829053</v>
@@ -677,39 +714,48 @@
         <v>10000</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3">
         <v>8423207</v>
       </c>
       <c r="L3">
+        <v>1203315.29</v>
+      </c>
+      <c r="M3">
         <v>7291127</v>
       </c>
-      <c r="M3">
+      <c r="N3">
+        <v>1041589.57</v>
+      </c>
+      <c r="O3">
         <v>1132079</v>
       </c>
-      <c r="R3" t="s">
-        <v>23</v>
+      <c r="P3">
+        <v>161725.57</v>
+      </c>
+      <c r="V3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
-        <v>6696207.86</v>
+        <v>7974043.061543</v>
       </c>
       <c r="C4" s="1">
-        <v>5796237.43</v>
+        <v>6150259.615152</v>
       </c>
       <c r="D4" s="1">
-        <v>899970.29</v>
+        <v>1823783.446391</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2">
         <v>40.901381</v>
@@ -721,42 +767,51 @@
         <v>80000</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K4">
         <v>46873455</v>
       </c>
       <c r="L4">
+        <v>6696207.86</v>
+      </c>
+      <c r="M4">
         <v>40573662</v>
       </c>
-      <c r="M4">
+      <c r="N4">
+        <v>5796237.43</v>
+      </c>
+      <c r="O4">
         <v>6299792</v>
       </c>
-      <c r="Q4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R4" t="s">
-        <v>29</v>
+      <c r="P4">
+        <v>899970.29</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1">
-        <v>3764857.14</v>
+        <v>5499822.268068</v>
       </c>
       <c r="C5" s="1">
-        <v>3162480</v>
+        <v>3641137.803452</v>
       </c>
       <c r="D5" s="1">
-        <v>602377.14</v>
+        <v>1858684.464616</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2">
         <v>40.866486</v>
@@ -765,48 +820,60 @@
         <v>71.968873</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K5">
         <v>26354000</v>
       </c>
       <c r="L5">
+        <v>3764857.14</v>
+      </c>
+      <c r="M5">
         <v>22137360</v>
       </c>
-      <c r="M5">
+      <c r="N5">
+        <v>3162480</v>
+      </c>
+      <c r="O5">
         <v>4216640</v>
       </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5">
+        <v>602377.14</v>
+      </c>
+      <c r="Q5" t="s">
         <v>34</v>
       </c>
-      <c r="P5" t="s">
-        <v>35</v>
-      </c>
       <c r="R5" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="U5" t="s">
+        <v>40</v>
+      </c>
+      <c r="V5" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1">
-        <v>2628857.14</v>
+        <v>3999266.267774</v>
       </c>
       <c r="C6" s="1">
-        <v>2208240</v>
+        <v>2582459.884578</v>
       </c>
       <c r="D6" s="1">
-        <v>420617.14</v>
+        <v>1416806.383196</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2">
         <v>40.850754</v>
@@ -815,36 +882,74 @@
         <v>72.04806</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K6">
         <v>18402000</v>
       </c>
       <c r="L6">
+        <v>2628857.14</v>
+      </c>
+      <c r="M6">
         <v>15457680</v>
       </c>
-      <c r="M6">
+      <c r="N6">
+        <v>2208240</v>
+      </c>
+      <c r="O6">
         <v>2944320</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6">
+        <v>420617.14</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S6" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" t="s">
         <v>40</v>
       </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R6" t="s">
-        <v>43</v>
+      <c r="V6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="1">
+        <v>856805.464158</v>
+      </c>
+      <c r="C7" s="1">
+        <v>557077.31197</v>
+      </c>
+      <c r="D7" s="1">
+        <v>299728.152188</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
